--- a/data/samples/v2/payroll_export.xlsx
+++ b/data/samples/v2/payroll_export.xlsx
@@ -1274,7 +1274,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>aadhya.menon@acmecorp.com</t>
+          <t>diya.menon@acmecorp.com</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>sai.joshi@acmecorp.com</t>
+          <t>diya.menon@acmecorp.com</t>
         </is>
       </c>
     </row>
